--- a/outputs/qc/qc_numeric_describe.xlsx
+++ b/outputs/qc/qc_numeric_describe.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,37 +485,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C2" t="n">
-        <v>104.2570860624062</v>
+        <v>104.2607434398414</v>
       </c>
       <c r="D2" t="n">
-        <v>0.221571381769898</v>
+        <v>0.2247468577920957</v>
       </c>
       <c r="E2" t="n">
-        <v>103.625887</v>
+        <v>103.625685</v>
       </c>
       <c r="F2" t="n">
-        <v>103.7743925</v>
+        <v>103.77437</v>
       </c>
       <c r="G2" t="n">
-        <v>103.8787162</v>
+        <v>103.878344</v>
       </c>
       <c r="H2" t="n">
-        <v>104.1083645</v>
+        <v>104.109887</v>
       </c>
       <c r="I2" t="n">
-        <v>104.233464</v>
+        <v>104.236568</v>
       </c>
       <c r="J2" t="n">
-        <v>104.416867</v>
+        <v>104.424583</v>
       </c>
       <c r="K2" t="n">
-        <v>104.6339699</v>
+        <v>104.6495678</v>
       </c>
       <c r="L2" t="n">
-        <v>104.69473804</v>
+        <v>104.69679092</v>
       </c>
       <c r="M2" t="n">
         <v>104.737231</v>
@@ -528,37 +528,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C3" t="n">
-        <v>26.87446342826506</v>
+        <v>26.87359421962339</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1778305741820512</v>
+        <v>0.179068423129197</v>
       </c>
       <c r="E3" t="n">
         <v>26.521204</v>
       </c>
       <c r="F3" t="n">
-        <v>26.54716894</v>
+        <v>26.54776076</v>
       </c>
       <c r="G3" t="n">
-        <v>26.6237582</v>
+        <v>26.62633</v>
       </c>
       <c r="H3" t="n">
-        <v>26.7425135</v>
+        <v>26.742254</v>
       </c>
       <c r="I3" t="n">
-        <v>26.852853</v>
+        <v>26.848504</v>
       </c>
       <c r="J3" t="n">
-        <v>26.969739</v>
+        <v>26.97016</v>
       </c>
       <c r="K3" t="n">
-        <v>27.2157815</v>
+        <v>27.218022</v>
       </c>
       <c r="L3" t="n">
-        <v>27.28613164</v>
+        <v>27.29083164</v>
       </c>
       <c r="M3" t="n">
         <v>27.357558</v>
@@ -571,40 +571,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C4" t="n">
-        <v>5.776959039245121</v>
+        <v>5.805012884043608</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9834176914687442</v>
+        <v>1.006321999129654</v>
       </c>
       <c r="E4" t="n">
         <v>3.73</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="G4" t="n">
         <v>4.61</v>
       </c>
       <c r="H4" t="n">
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
       <c r="I4" t="n">
-        <v>5.52</v>
+        <v>5.53</v>
       </c>
       <c r="J4" t="n">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="K4" t="n">
-        <v>7.91</v>
+        <v>7.97</v>
       </c>
       <c r="L4" t="n">
-        <v>8.333800000000002</v>
+        <v>8.385600000000005</v>
       </c>
       <c r="M4" t="n">
-        <v>8.720000000000001</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="5">
@@ -614,641 +614,770 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03007523170114356</v>
+        <v>0.04094119437750542</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0327378834469154</v>
+        <v>0.07221247691458729</v>
       </c>
       <c r="E5" t="n">
         <v>0.00024390243902439</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001234558912753304</v>
+        <v>0.001244235255258973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002929238395563136</v>
+        <v>0.002867924936924058</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00892857142857143</v>
+        <v>0.00909090909090909</v>
       </c>
       <c r="I5" t="n">
-        <v>0.019327731092437</v>
+        <v>0.0203921568627451</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0389982518811279</v>
+        <v>0.0435323383084577</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0939445104361105</v>
+        <v>0.1410077594256094</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1746951220929284</v>
+        <v>0.3594238310708912</v>
       </c>
       <c r="M5" t="n">
-        <v>0.251989389920424</v>
+        <v>1.82030338389732</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>altitude</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C6" t="n">
-        <v>1206.098404457517</v>
+        <v>2159.180773042616</v>
       </c>
       <c r="D6" t="n">
-        <v>556.748771305457</v>
+        <v>214.1270306077965</v>
       </c>
       <c r="E6" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>233.62</v>
+        <v>1653.88</v>
       </c>
       <c r="G6" t="n">
-        <v>417.1</v>
+        <v>1822</v>
       </c>
       <c r="H6" t="n">
-        <v>804</v>
+        <v>2061</v>
       </c>
       <c r="I6" t="n">
-        <v>1139</v>
+        <v>2179</v>
       </c>
       <c r="J6" t="n">
-        <v>1569</v>
+        <v>2284</v>
       </c>
       <c r="K6" t="n">
-        <v>2119.9</v>
+        <v>2442</v>
       </c>
       <c r="L6" t="n">
-        <v>2634.360000000002</v>
+        <v>2562.56</v>
       </c>
       <c r="M6" t="n">
-        <v>5883</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>geology</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C7" t="n">
-        <v>2005.884838087068</v>
+        <v>66.64281466798811</v>
       </c>
       <c r="D7" t="n">
-        <v>746.1893757934288</v>
+        <v>18.58548818676303</v>
       </c>
       <c r="E7" t="n">
-        <v>394</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>706</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>984</v>
+        <v>37</v>
       </c>
       <c r="H7" t="n">
-        <v>1511</v>
+        <v>56</v>
       </c>
       <c r="I7" t="n">
-        <v>1901</v>
+        <v>61</v>
       </c>
       <c r="J7" t="n">
-        <v>2373.5</v>
+        <v>79</v>
       </c>
       <c r="K7" t="n">
-        <v>3419.199999999997</v>
+        <v>87</v>
       </c>
       <c r="L7" t="n">
-        <v>4306.820000000004</v>
+        <v>97</v>
       </c>
       <c r="M7" t="n">
-        <v>6296</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C8" t="n">
-        <v>1187.878190006434</v>
+        <v>1207.602350839524</v>
       </c>
       <c r="D8" t="n">
-        <v>440.951932992435</v>
+        <v>557.6122474658027</v>
       </c>
       <c r="E8" t="n">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="F8" t="n">
-        <v>397</v>
+        <v>233</v>
       </c>
       <c r="G8" t="n">
-        <v>548</v>
+        <v>417</v>
       </c>
       <c r="H8" t="n">
-        <v>880</v>
+        <v>802</v>
       </c>
       <c r="I8" t="n">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="J8" t="n">
-        <v>1452.5</v>
+        <v>1571</v>
       </c>
       <c r="K8" t="n">
-        <v>1969.799999999999</v>
+        <v>2125</v>
       </c>
       <c r="L8" t="n">
-        <v>2370.76</v>
+        <v>2649.120000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>4634</v>
+        <v>5883</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C9" t="n">
-        <v>1.126414604331975</v>
+        <v>2000.321902874133</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5435209846294932</v>
+        <v>744.4366006217775</v>
       </c>
       <c r="E9" t="n">
-        <v>0.18</v>
+        <v>394</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3431</v>
+        <v>694.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.51</v>
+        <v>978</v>
       </c>
       <c r="H9" t="n">
-        <v>0.78</v>
+        <v>1505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.99</v>
+        <v>1895</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>2369</v>
       </c>
       <c r="K9" t="n">
-        <v>2.28</v>
+        <v>3415.200000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>2.913800000000001</v>
+        <v>4273.880000000009</v>
       </c>
       <c r="M9" t="n">
-        <v>3.66</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C10" t="n">
-        <v>4.02994880763457</v>
+        <v>1186.61189296333</v>
       </c>
       <c r="D10" t="n">
-        <v>1.839704887330466</v>
+        <v>442.9872260145413</v>
       </c>
       <c r="E10" t="n">
-        <v>0.48</v>
+        <v>161</v>
       </c>
       <c r="F10" t="n">
-        <v>1.22</v>
+        <v>385.88</v>
       </c>
       <c r="G10" t="n">
-        <v>1.74</v>
+        <v>540</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>874</v>
       </c>
       <c r="I10" t="n">
-        <v>3.68</v>
+        <v>1141</v>
       </c>
       <c r="J10" t="n">
-        <v>4.84</v>
+        <v>1453</v>
       </c>
       <c r="K10" t="n">
-        <v>7.47699999999999</v>
+        <v>1968</v>
       </c>
       <c r="L10" t="n">
-        <v>10.31900000000001</v>
+        <v>2381.960000000006</v>
       </c>
       <c r="M10" t="n">
-        <v>23.24</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C11" t="n">
-        <v>19.15655157623847</v>
+        <v>1.131259920713578</v>
       </c>
       <c r="D11" t="n">
-        <v>1.404950244179447</v>
+        <v>0.5477263984370294</v>
       </c>
       <c r="E11" t="n">
-        <v>15.16</v>
+        <v>0.18</v>
       </c>
       <c r="F11" t="n">
-        <v>16.4662</v>
+        <v>0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>17.111</v>
+        <v>0.51</v>
       </c>
       <c r="H11" t="n">
-        <v>18.12</v>
+        <v>0.78</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>0.99</v>
       </c>
       <c r="J11" t="n">
-        <v>20.05</v>
+        <v>1.31</v>
       </c>
       <c r="K11" t="n">
-        <v>21.67899999999999</v>
+        <v>2.308000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>22.8676</v>
+        <v>2.92</v>
       </c>
       <c r="M11" t="n">
-        <v>25.28</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C12" t="n">
-        <v>29.3326807965044</v>
+        <v>4.016755458870168</v>
       </c>
       <c r="D12" t="n">
-        <v>4.068935906235075</v>
+        <v>1.829818681346361</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08377979000000001</v>
+        <v>0.48</v>
       </c>
       <c r="F12" t="n">
-        <v>21.3703941966</v>
+        <v>1.2044</v>
       </c>
       <c r="G12" t="n">
-        <v>23.74515686</v>
+        <v>1.74</v>
       </c>
       <c r="H12" t="n">
-        <v>26.9160553</v>
+        <v>2.81</v>
       </c>
       <c r="I12" t="n">
-        <v>29.21772156</v>
+        <v>3.68</v>
       </c>
       <c r="J12" t="n">
-        <v>31.830767825</v>
+        <v>4.84</v>
       </c>
       <c r="K12" t="n">
-        <v>35.6561676</v>
+        <v>7.45</v>
       </c>
       <c r="L12" t="n">
-        <v>38.460931944</v>
+        <v>10.26</v>
       </c>
       <c r="M12" t="n">
-        <v>41.13704834</v>
+        <v>23.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Particle content</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C13" t="n">
-        <v>44.70256058331546</v>
+        <v>19.15469375619425</v>
       </c>
       <c r="D13" t="n">
-        <v>2.540840913887724</v>
+        <v>1.401514436059512</v>
       </c>
       <c r="E13" t="n">
-        <v>36.1</v>
+        <v>15.16</v>
       </c>
       <c r="F13" t="n">
-        <v>38.71</v>
+        <v>16.4644</v>
       </c>
       <c r="G13" t="n">
-        <v>40.44</v>
+        <v>17.11</v>
       </c>
       <c r="H13" t="n">
-        <v>42.96</v>
+        <v>18.13</v>
       </c>
       <c r="I13" t="n">
-        <v>44.79</v>
+        <v>19</v>
       </c>
       <c r="J13" t="n">
-        <v>46.56</v>
+        <v>20.05</v>
       </c>
       <c r="K13" t="n">
-        <v>48.67</v>
+        <v>21.64</v>
       </c>
       <c r="L13" t="n">
-        <v>49.94520000000001</v>
+        <v>22.85120000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>51.68</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>water content</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C14" t="n">
-        <v>27.95211022946601</v>
+        <v>29.32918100651735</v>
       </c>
       <c r="D14" t="n">
-        <v>3.141810721662825</v>
+        <v>4.066952278286077</v>
       </c>
       <c r="E14" t="n">
-        <v>20.58</v>
+        <v>0.08377979000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>21.7286</v>
+        <v>21.42057788</v>
       </c>
       <c r="G14" t="n">
-        <v>22.691</v>
+        <v>23.79250488</v>
       </c>
       <c r="H14" t="n">
-        <v>25.92</v>
+        <v>26.9160553</v>
       </c>
       <c r="I14" t="n">
-        <v>28.09</v>
+        <v>29.19772949</v>
       </c>
       <c r="J14" t="n">
-        <v>30.005</v>
+        <v>31.82392578</v>
       </c>
       <c r="K14" t="n">
-        <v>33.02</v>
+        <v>35.668538208</v>
       </c>
       <c r="L14" t="n">
-        <v>35.5214</v>
+        <v>38.39956762400005</v>
       </c>
       <c r="M14" t="n">
-        <v>38.78</v>
+        <v>41.13704834</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>Particle content</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C15" t="n">
-        <v>27.33026163414111</v>
+        <v>44.70363131813676</v>
       </c>
       <c r="D15" t="n">
-        <v>1.747438640403366</v>
+        <v>2.540677305863943</v>
       </c>
       <c r="E15" t="n">
-        <v>22.25</v>
+        <v>36.1</v>
       </c>
       <c r="F15" t="n">
-        <v>23.52</v>
+        <v>38.6508</v>
       </c>
       <c r="G15" t="n">
-        <v>24.73</v>
+        <v>40.422</v>
       </c>
       <c r="H15" t="n">
-        <v>26.14</v>
+        <v>42.97</v>
       </c>
       <c r="I15" t="n">
-        <v>27.2</v>
+        <v>44.79</v>
       </c>
       <c r="J15" t="n">
-        <v>28.425</v>
+        <v>46.56</v>
       </c>
       <c r="K15" t="n">
-        <v>30.34</v>
+        <v>48.68</v>
       </c>
       <c r="L15" t="n">
-        <v>32.0576</v>
+        <v>49.93</v>
       </c>
       <c r="M15" t="n">
-        <v>34.8</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>soil type</t>
+          <t>clay content</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C16" t="n">
-        <v>55.59939952820073</v>
+        <v>27.95759167492567</v>
       </c>
       <c r="D16" t="n">
-        <v>32.73103761447504</v>
+        <v>3.142912076427326</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>20.58</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>21.6744</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>22.702</v>
       </c>
       <c r="H16" t="n">
-        <v>53</v>
+        <v>25.9</v>
       </c>
       <c r="I16" t="n">
-        <v>58</v>
+        <v>28.1</v>
       </c>
       <c r="J16" t="n">
-        <v>58</v>
+        <v>30.02</v>
       </c>
       <c r="K16" t="n">
-        <v>77</v>
+        <v>33.03</v>
       </c>
       <c r="L16" t="n">
-        <v>184</v>
+        <v>35.54</v>
       </c>
       <c r="M16" t="n">
-        <v>184</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bulk density</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C17" t="n">
-        <v>1.254496078432652</v>
+        <v>27.32371655104063</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02163728150390935</v>
+        <v>1.746253177953383</v>
       </c>
       <c r="E17" t="n">
-        <v>1.16794836403435</v>
+        <v>22.25</v>
       </c>
       <c r="F17" t="n">
-        <v>1.20517283057986</v>
+        <v>23.52</v>
       </c>
       <c r="G17" t="n">
-        <v>1.219745331561763</v>
+        <v>24.732</v>
       </c>
       <c r="H17" t="n">
-        <v>1.24014145412446</v>
+        <v>26.14</v>
       </c>
       <c r="I17" t="n">
-        <v>1.25466419970019</v>
+        <v>27.19</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2687007074766</v>
+        <v>28.4</v>
       </c>
       <c r="K17" t="n">
-        <v>1.289719701686266</v>
+        <v>30.348</v>
       </c>
       <c r="L17" t="n">
-        <v>1.304915211392771</v>
+        <v>32.06120000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>1.34228109957259</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vegetation cover type</t>
+          <t>Land use type</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
       <c r="C18" t="n">
-        <v>117.76238473086</v>
+        <v>1.204757185332012</v>
       </c>
       <c r="D18" t="n">
-        <v>33.71106035658082</v>
+        <v>0.7228410425466</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>130</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>130</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>210</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>soil type</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5045</v>
+      </c>
+      <c r="C19" t="n">
+        <v>55.52507433102081</v>
+      </c>
+      <c r="D19" t="n">
+        <v>32.81350976497605</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>53</v>
+      </c>
+      <c r="I19" t="n">
+        <v>58</v>
+      </c>
+      <c r="J19" t="n">
+        <v>58</v>
+      </c>
+      <c r="K19" t="n">
+        <v>77</v>
+      </c>
+      <c r="L19" t="n">
+        <v>184</v>
+      </c>
+      <c r="M19" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>bulk density</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5045</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.254521515759072</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.02160020006241458</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.16794836403435</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.204846830967883</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.219905162769734</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.24019731146427</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.25474520107668</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.26871592464216</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.289650952053966</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.304797905044763</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.34228109957259</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vegetation cover type</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5045</v>
+      </c>
+      <c r="C21" t="n">
+        <v>117.58414271556</v>
+      </c>
+      <c r="D21" t="n">
+        <v>33.94499659300173</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>130</v>
+      </c>
+      <c r="I21" t="n">
+        <v>130</v>
+      </c>
+      <c r="J21" t="n">
+        <v>130</v>
+      </c>
+      <c r="K21" t="n">
+        <v>130</v>
+      </c>
+      <c r="L21" t="n">
+        <v>130</v>
+      </c>
+      <c r="M21" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Distance from pollution source</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>4663</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4905.118242486657</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4507.62157820784</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="B22" t="n">
+        <v>5045</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4905.124429003549</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4529.106576463952</v>
+      </c>
+      <c r="E22" t="n">
         <v>35.14183780678301</v>
       </c>
-      <c r="F19" t="n">
-        <v>182.4223522275876</v>
-      </c>
-      <c r="G19" t="n">
-        <v>460.9039651364092</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1670.591893666664</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3482.976879018961</v>
-      </c>
-      <c r="J19" t="n">
-        <v>6487.988755167826</v>
-      </c>
-      <c r="K19" t="n">
-        <v>14630.09529128736</v>
-      </c>
-      <c r="L19" t="n">
-        <v>20322.46959669903</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="F22" t="n">
+        <v>162.2669898395631</v>
+      </c>
+      <c r="G22" t="n">
+        <v>428.8768442386324</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1622.482524409271</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3484.028054262728</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6522.438729913969</v>
+      </c>
+      <c r="K22" t="n">
+        <v>14688.93802574827</v>
+      </c>
+      <c r="L22" t="n">
+        <v>20282.66321755079</v>
+      </c>
+      <c r="M22" t="n">
         <v>23260.1946129376</v>
       </c>
     </row>
